--- a/data/base/Backlog_36.xlsx
+++ b/data/base/Backlog_36.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{5DE4159D-846A-43D7-929B-965D42C26CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6E8D15A-A390-4732-9901-5ECB41A21B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{65FB71B2-8070-41A1-B8B8-22F4C136B45C}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{65FB71B2-8070-41A1-B8B8-22F4C136B45C}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="1" r:id="rId1"/>
     <sheet name="SPN" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="29">
   <si>
     <t>Status</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>Maria Oliveira</t>
-  </si>
-  <si>
-    <t>Jose Ortiz</t>
   </si>
   <si>
     <t>Higor Jesus</t>
@@ -110,11 +107,20 @@
   <si>
     <t>Willian Rios</t>
   </si>
+  <si>
+    <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Felipe Nascimento</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-416]mmm/yy"/>
+  </numFmts>
   <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -264,7 +270,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -442,6 +448,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -620,37 +638,50 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="33" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="21" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="46" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="34" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="21" fontId="0" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1031,15 +1062,15 @@
   <cols>
     <col min="1" max="1" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" style="11" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="15.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="40.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="26.28515625" style="2" bestFit="1" customWidth="1"/>
@@ -1082,42 +1113,42 @@
   <sheetData>
     <row r="1" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>5</v>
@@ -1128,36 +1159,36 @@
       <c r="D2" s="3">
         <v>36</v>
       </c>
-      <c r="E2" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F2" s="11">
+      <c r="E2" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F2" s="5">
         <v>46283</v>
       </c>
       <c r="G2" s="3">
         <v>24002</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <v>46262.633275462962</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="5">
         <v>46279</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L2" s="7"/>
-      <c r="M2" s="8"/>
-      <c r="O2" s="7"/>
-      <c r="AS2" s="8"/>
-      <c r="AT2" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="8"/>
+      <c r="M2" s="9"/>
+      <c r="O2" s="8"/>
+      <c r="AS2" s="9"/>
+      <c r="AT2" s="8"/>
     </row>
     <row r="3" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>5</v>
@@ -1168,76 +1199,76 @@
       <c r="D3" s="3">
         <v>36</v>
       </c>
-      <c r="E3" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F3" s="11">
+      <c r="E3" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F3" s="5">
         <v>46283</v>
       </c>
       <c r="G3" s="3">
         <v>24703</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="6">
         <v>46274.629293981481</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="5">
         <v>46279</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="7"/>
-      <c r="M3" s="8"/>
-      <c r="O3" s="7"/>
-      <c r="AS3" s="8"/>
-      <c r="AT3" s="7"/>
-    </row>
-    <row r="4" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="9"/>
+      <c r="O3" s="8"/>
+      <c r="AS3" s="9"/>
+      <c r="AT3" s="8"/>
+    </row>
+    <row r="4" spans="1:46" s="20" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D4" s="3">
-        <v>36</v>
-      </c>
-      <c r="E4" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F4" s="11">
-        <v>46283</v>
-      </c>
-      <c r="G4" s="3">
+      <c r="C4" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D4" s="13">
+        <v>36</v>
+      </c>
+      <c r="E4" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F4" s="15">
+        <v>46283</v>
+      </c>
+      <c r="G4" s="13">
         <v>22708</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="16">
         <v>46241.641284722224</v>
       </c>
-      <c r="I4" s="11">
-        <v>46279</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="7"/>
-      <c r="M4" s="8"/>
-      <c r="O4" s="7"/>
-      <c r="AS4" s="8"/>
-      <c r="AT4" s="7"/>
+      <c r="I4" s="15">
+        <v>46279</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="18"/>
+      <c r="M4" s="19"/>
+      <c r="O4" s="18"/>
+      <c r="AS4" s="19"/>
+      <c r="AT4" s="18"/>
     </row>
     <row r="5" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>4</v>
@@ -1248,35 +1279,35 @@
       <c r="D5" s="3">
         <v>36</v>
       </c>
-      <c r="E5" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F5" s="11">
+      <c r="E5" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F5" s="5">
         <v>46283</v>
       </c>
       <c r="G5" s="3">
         <v>23825</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>46260.340439814812</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="5">
         <v>46279</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="8"/>
-      <c r="AS5" s="8"/>
-      <c r="AT5" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="8"/>
+      <c r="M5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="8"/>
     </row>
     <row r="6" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>4</v>
@@ -1287,36 +1318,36 @@
       <c r="D6" s="3">
         <v>36</v>
       </c>
-      <c r="E6" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F6" s="11">
+      <c r="E6" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F6" s="5">
         <v>46283</v>
       </c>
       <c r="G6" s="3">
         <v>24087</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="6">
         <v>46265.438564814816</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="5">
         <v>46279</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="8"/>
-      <c r="O6" s="7"/>
-      <c r="AS6" s="8"/>
-      <c r="AT6" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="8"/>
+      <c r="M6" s="9"/>
+      <c r="O6" s="8"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="8"/>
     </row>
     <row r="7" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>4</v>
@@ -1327,36 +1358,36 @@
       <c r="D7" s="3">
         <v>36</v>
       </c>
-      <c r="E7" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F7" s="11">
+      <c r="E7" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F7" s="5">
         <v>46283</v>
       </c>
       <c r="G7" s="3">
         <v>24317</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <v>46267.638969907406</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="5">
         <v>46279</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L7" s="7"/>
-      <c r="M7" s="8"/>
-      <c r="O7" s="7"/>
-      <c r="AS7" s="8"/>
-      <c r="AT7" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="8"/>
+      <c r="M7" s="9"/>
+      <c r="O7" s="8"/>
+      <c r="AS7" s="9"/>
+      <c r="AT7" s="8"/>
     </row>
     <row r="8" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>4</v>
@@ -1367,162 +1398,162 @@
       <c r="D8" s="3">
         <v>36</v>
       </c>
-      <c r="E8" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F8" s="11">
+      <c r="E8" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F8" s="5">
         <v>46283</v>
       </c>
       <c r="G8" s="3">
         <v>24376</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="6">
         <v>46268.473703703705</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="5">
         <v>46279</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L8" s="7"/>
-      <c r="M8" s="8"/>
-      <c r="O8" s="7"/>
-      <c r="AS8" s="8"/>
-      <c r="AT8" s="7"/>
-    </row>
-    <row r="9" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="8"/>
+      <c r="M8" s="9"/>
+      <c r="O8" s="8"/>
+      <c r="AS8" s="9"/>
+      <c r="AT8" s="8"/>
+    </row>
+    <row r="9" spans="1:46" s="20" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D9" s="3">
-        <v>36</v>
-      </c>
-      <c r="E9" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F9" s="11">
-        <v>46283</v>
-      </c>
-      <c r="G9" s="3">
+      <c r="C9" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D9" s="13">
+        <v>36</v>
+      </c>
+      <c r="E9" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F9" s="15">
+        <v>46283</v>
+      </c>
+      <c r="G9" s="13">
         <v>24470</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9" s="16">
         <v>46269.639328703706</v>
       </c>
-      <c r="I9" s="11">
-        <v>46279</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L9" s="7"/>
-      <c r="M9" s="8"/>
-      <c r="O9" s="7"/>
-      <c r="Y9" s="7"/>
-      <c r="Z9" s="7"/>
-      <c r="AS9" s="8"/>
-      <c r="AT9" s="7"/>
-    </row>
-    <row r="10" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="4" t="s">
+      <c r="I9" s="15">
+        <v>46279</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L9" s="18"/>
+      <c r="M9" s="19"/>
+      <c r="O9" s="18"/>
+      <c r="Y9" s="18"/>
+      <c r="Z9" s="18"/>
+      <c r="AS9" s="19"/>
+      <c r="AT9" s="18"/>
+    </row>
+    <row r="10" spans="1:46" s="20" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D10" s="3">
-        <v>36</v>
-      </c>
-      <c r="E10" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F10" s="11">
-        <v>46283</v>
-      </c>
-      <c r="G10" s="3">
+      <c r="C10" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D10" s="13">
+        <v>36</v>
+      </c>
+      <c r="E10" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F10" s="15">
+        <v>46283</v>
+      </c>
+      <c r="G10" s="13">
         <v>24571</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10" s="16">
         <v>46273.551944444444</v>
       </c>
-      <c r="I10" s="11">
-        <v>46279</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L10" s="7"/>
-      <c r="M10" s="8"/>
-      <c r="O10" s="7"/>
-      <c r="Y10" s="7"/>
-      <c r="Z10" s="7"/>
-      <c r="AS10" s="8"/>
-      <c r="AT10" s="7"/>
-    </row>
-    <row r="11" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="4" t="s">
+      <c r="I10" s="15">
+        <v>46279</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="19"/>
+      <c r="O10" s="18"/>
+      <c r="Y10" s="18"/>
+      <c r="Z10" s="18"/>
+      <c r="AS10" s="19"/>
+      <c r="AT10" s="18"/>
+    </row>
+    <row r="11" spans="1:46" s="20" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C11" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D11" s="3">
-        <v>36</v>
-      </c>
-      <c r="E11" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F11" s="11">
-        <v>46283</v>
-      </c>
-      <c r="G11" s="3">
+      <c r="C11" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D11" s="13">
+        <v>36</v>
+      </c>
+      <c r="E11" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F11" s="15">
+        <v>46283</v>
+      </c>
+      <c r="G11" s="13">
         <v>24622</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11" s="16">
         <v>46273.697280092594</v>
       </c>
-      <c r="I11" s="11">
-        <v>46279</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L11" s="7"/>
-      <c r="M11" s="8"/>
-      <c r="O11" s="7"/>
-      <c r="Y11" s="7"/>
-      <c r="Z11" s="7"/>
-      <c r="AS11" s="8"/>
-      <c r="AT11" s="7"/>
+      <c r="I11" s="15">
+        <v>46279</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L11" s="18"/>
+      <c r="M11" s="19"/>
+      <c r="O11" s="18"/>
+      <c r="Y11" s="18"/>
+      <c r="Z11" s="18"/>
+      <c r="AS11" s="19"/>
+      <c r="AT11" s="18"/>
     </row>
     <row r="12" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>4</v>
@@ -1533,36 +1564,36 @@
       <c r="D12" s="3">
         <v>36</v>
       </c>
-      <c r="E12" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F12" s="11">
+      <c r="E12" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F12" s="5">
         <v>46283</v>
       </c>
       <c r="G12" s="3">
         <v>24687</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12" s="6">
         <v>46274.519108796296</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="5">
         <v>46279</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L12" s="7"/>
-      <c r="M12" s="8"/>
-      <c r="O12" s="7"/>
-      <c r="AS12" s="8"/>
-      <c r="AT12" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="8"/>
+      <c r="M12" s="9"/>
+      <c r="O12" s="8"/>
+      <c r="AS12" s="9"/>
+      <c r="AT12" s="8"/>
     </row>
     <row r="13" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>7</v>
@@ -1573,116 +1604,116 @@
       <c r="D13" s="3">
         <v>36</v>
       </c>
-      <c r="E13" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F13" s="11">
+      <c r="E13" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F13" s="5">
         <v>46283</v>
       </c>
       <c r="G13" s="3">
         <v>24508</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="6">
         <v>46272.692384259259</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="5">
         <v>46279</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="8"/>
-      <c r="O13" s="7"/>
-      <c r="AS13" s="8"/>
-      <c r="AT13" s="7"/>
-    </row>
-    <row r="14" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D14" s="3">
-        <v>36</v>
-      </c>
-      <c r="E14" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F14" s="11">
-        <v>46283</v>
-      </c>
-      <c r="G14" s="3">
+        <v>27</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="8"/>
+      <c r="M13" s="9"/>
+      <c r="O13" s="8"/>
+      <c r="AS13" s="9"/>
+      <c r="AT13" s="8"/>
+    </row>
+    <row r="14" spans="1:46" s="20" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D14" s="13">
+        <v>36</v>
+      </c>
+      <c r="E14" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F14" s="15">
+        <v>46283</v>
+      </c>
+      <c r="G14" s="13">
         <v>24579</v>
       </c>
-      <c r="H14" s="5">
+      <c r="H14" s="16">
         <v>46273.576782407406</v>
       </c>
-      <c r="I14" s="11">
-        <v>46279</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="7"/>
-      <c r="M14" s="8"/>
-      <c r="O14" s="7"/>
-      <c r="AS14" s="8"/>
-      <c r="AT14" s="7"/>
-    </row>
-    <row r="15" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="I14" s="15">
+        <v>46279</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L14" s="18"/>
+      <c r="M14" s="19"/>
+      <c r="O14" s="18"/>
+      <c r="AS14" s="19"/>
+      <c r="AT14" s="18"/>
+    </row>
+    <row r="15" spans="1:46" s="20" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D15" s="3">
-        <v>36</v>
-      </c>
-      <c r="E15" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F15" s="11">
-        <v>46283</v>
-      </c>
-      <c r="G15" s="3">
+      <c r="C15" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D15" s="13">
+        <v>36</v>
+      </c>
+      <c r="E15" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F15" s="15">
+        <v>46283</v>
+      </c>
+      <c r="G15" s="13">
         <v>22680</v>
       </c>
-      <c r="H15" s="5">
+      <c r="H15" s="16">
         <v>46241.559837962966</v>
       </c>
-      <c r="I15" s="11">
-        <v>46279</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="8"/>
-      <c r="O15" s="7"/>
-      <c r="AS15" s="8"/>
-      <c r="AT15" s="7"/>
+      <c r="I15" s="15">
+        <v>46279</v>
+      </c>
+      <c r="J15" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L15" s="18"/>
+      <c r="M15" s="19"/>
+      <c r="O15" s="18"/>
+      <c r="AS15" s="19"/>
+      <c r="AT15" s="18"/>
     </row>
     <row r="16" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>2</v>
@@ -1693,36 +1724,36 @@
       <c r="D16" s="3">
         <v>36</v>
       </c>
-      <c r="E16" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F16" s="11">
+      <c r="E16" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F16" s="5">
         <v>46283</v>
       </c>
       <c r="G16" s="3">
         <v>22720</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="6">
         <v>46241.683159722219</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="5">
         <v>46279</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L16" s="7"/>
-      <c r="M16" s="8"/>
-      <c r="O16" s="7"/>
-      <c r="AS16" s="8"/>
-      <c r="AT16" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L16" s="8"/>
+      <c r="M16" s="9"/>
+      <c r="O16" s="8"/>
+      <c r="AS16" s="9"/>
+      <c r="AT16" s="8"/>
     </row>
     <row r="17" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -1733,38 +1764,38 @@
       <c r="D17" s="3">
         <v>36</v>
       </c>
-      <c r="E17" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F17" s="11">
+      <c r="E17" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F17" s="5">
         <v>46283</v>
       </c>
       <c r="G17" s="3">
         <v>24313</v>
       </c>
-      <c r="H17" s="5">
+      <c r="H17" s="6">
         <v>46267.634421296294</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="5">
         <v>46279</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="8"/>
-      <c r="O17" s="7"/>
-      <c r="Y17" s="7"/>
-      <c r="Z17" s="7"/>
-      <c r="AS17" s="8"/>
-      <c r="AT17" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L17" s="8"/>
+      <c r="M17" s="9"/>
+      <c r="O17" s="8"/>
+      <c r="Y17" s="8"/>
+      <c r="Z17" s="8"/>
+      <c r="AS17" s="9"/>
+      <c r="AT17" s="8"/>
     </row>
     <row r="18" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -1775,36 +1806,36 @@
       <c r="D18" s="3">
         <v>36</v>
       </c>
-      <c r="E18" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F18" s="11">
+      <c r="E18" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F18" s="5">
         <v>46283</v>
       </c>
       <c r="G18" s="3">
         <v>24314</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="6">
         <v>46267.635115740741</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="5">
         <v>46279</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="7"/>
-      <c r="M18" s="8"/>
-      <c r="O18" s="7"/>
-      <c r="AS18" s="8"/>
-      <c r="AT18" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="8"/>
+      <c r="M18" s="9"/>
+      <c r="O18" s="8"/>
+      <c r="AS18" s="9"/>
+      <c r="AT18" s="8"/>
     </row>
     <row r="19" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>2</v>
@@ -1815,36 +1846,36 @@
       <c r="D19" s="3">
         <v>36</v>
       </c>
-      <c r="E19" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F19" s="11">
+      <c r="E19" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F19" s="5">
         <v>46283</v>
       </c>
       <c r="G19" s="3">
         <v>24315</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="6">
         <v>46267.635960648149</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="5">
         <v>46279</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="8"/>
-      <c r="O19" s="7"/>
-      <c r="AS19" s="8"/>
-      <c r="AT19" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L19" s="8"/>
+      <c r="M19" s="9"/>
+      <c r="O19" s="8"/>
+      <c r="AS19" s="9"/>
+      <c r="AT19" s="8"/>
     </row>
     <row r="20" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>2</v>
@@ -1855,36 +1886,36 @@
       <c r="D20" s="3">
         <v>36</v>
       </c>
-      <c r="E20" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F20" s="11">
+      <c r="E20" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F20" s="5">
         <v>46283</v>
       </c>
       <c r="G20" s="3">
         <v>24316</v>
       </c>
-      <c r="H20" s="5">
+      <c r="H20" s="6">
         <v>46267.636863425927</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="5">
         <v>46279</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L20" s="7"/>
-      <c r="M20" s="8"/>
-      <c r="O20" s="7"/>
-      <c r="AS20" s="8"/>
-      <c r="AT20" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L20" s="8"/>
+      <c r="M20" s="9"/>
+      <c r="O20" s="8"/>
+      <c r="AS20" s="9"/>
+      <c r="AT20" s="8"/>
     </row>
     <row r="21" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>2</v>
@@ -1895,36 +1926,36 @@
       <c r="D21" s="3">
         <v>36</v>
       </c>
-      <c r="E21" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F21" s="11">
+      <c r="E21" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F21" s="5">
         <v>46283</v>
       </c>
       <c r="G21" s="3">
         <v>24444</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="6">
         <v>46269.430520833332</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="5">
         <v>46279</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="8"/>
-      <c r="O21" s="7"/>
-      <c r="AS21" s="8"/>
-      <c r="AT21" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L21" s="8"/>
+      <c r="M21" s="9"/>
+      <c r="O21" s="8"/>
+      <c r="AS21" s="9"/>
+      <c r="AT21" s="8"/>
     </row>
     <row r="22" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>2</v>
@@ -1935,36 +1966,36 @@
       <c r="D22" s="3">
         <v>36</v>
       </c>
-      <c r="E22" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F22" s="11">
+      <c r="E22" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F22" s="5">
         <v>46283</v>
       </c>
       <c r="G22" s="3">
         <v>24520</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="6">
         <v>46273.339618055557</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="5">
         <v>46279</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" s="7"/>
-      <c r="M22" s="8"/>
-      <c r="O22" s="7"/>
-      <c r="AS22" s="8"/>
-      <c r="AT22" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="8"/>
+      <c r="M22" s="9"/>
+      <c r="O22" s="8"/>
+      <c r="AS22" s="9"/>
+      <c r="AT22" s="8"/>
     </row>
     <row r="23" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>2</v>
@@ -1975,36 +2006,36 @@
       <c r="D23" s="3">
         <v>36</v>
       </c>
-      <c r="E23" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F23" s="11">
+      <c r="E23" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F23" s="5">
         <v>46283</v>
       </c>
       <c r="G23" s="3">
         <v>24582</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="6">
         <v>46273.590185185189</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="5">
         <v>46279</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="9"/>
-      <c r="O23" s="7"/>
-      <c r="AS23" s="8"/>
-      <c r="AT23" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L23" s="8"/>
+      <c r="M23" s="10"/>
+      <c r="O23" s="8"/>
+      <c r="AS23" s="9"/>
+      <c r="AT23" s="8"/>
     </row>
     <row r="24" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>2</v>
@@ -2015,35 +2046,35 @@
       <c r="D24" s="3">
         <v>36</v>
       </c>
-      <c r="E24" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F24" s="11">
+      <c r="E24" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F24" s="5">
         <v>46283</v>
       </c>
       <c r="G24" s="3">
         <v>24589</v>
       </c>
-      <c r="H24" s="5">
+      <c r="H24" s="6">
         <v>46273.603101851855</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="5">
         <v>46279</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" s="7"/>
-      <c r="M24" s="8"/>
-      <c r="AS24" s="8"/>
-      <c r="AT24" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="8"/>
+      <c r="M24" s="9"/>
+      <c r="AS24" s="9"/>
+      <c r="AT24" s="8"/>
     </row>
     <row r="25" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>2</v>
@@ -2054,35 +2085,35 @@
       <c r="D25" s="3">
         <v>36</v>
       </c>
-      <c r="E25" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F25" s="11">
+      <c r="E25" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F25" s="5">
         <v>46283</v>
       </c>
       <c r="G25" s="3">
         <v>24591</v>
       </c>
-      <c r="H25" s="5">
+      <c r="H25" s="6">
         <v>46273.607511574075</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="5">
         <v>46279</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="7"/>
-      <c r="M25" s="8"/>
-      <c r="AS25" s="8"/>
-      <c r="AT25" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L25" s="8"/>
+      <c r="M25" s="9"/>
+      <c r="AS25" s="9"/>
+      <c r="AT25" s="8"/>
     </row>
     <row r="26" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>2</v>
@@ -2093,36 +2124,36 @@
       <c r="D26" s="3">
         <v>36</v>
       </c>
-      <c r="E26" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F26" s="11">
+      <c r="E26" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F26" s="5">
         <v>46283</v>
       </c>
       <c r="G26" s="3">
         <v>24602</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H26" s="6">
         <v>46273.643935185188</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="5">
         <v>46279</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="7"/>
-      <c r="M26" s="8"/>
-      <c r="O26" s="7"/>
-      <c r="AS26" s="8"/>
-      <c r="AT26" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L26" s="8"/>
+      <c r="M26" s="9"/>
+      <c r="O26" s="8"/>
+      <c r="AS26" s="9"/>
+      <c r="AT26" s="8"/>
     </row>
     <row r="27" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>2</v>
@@ -2133,35 +2164,35 @@
       <c r="D27" s="3">
         <v>36</v>
       </c>
-      <c r="E27" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F27" s="11">
+      <c r="E27" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F27" s="5">
         <v>46283</v>
       </c>
       <c r="G27" s="3">
         <v>24615</v>
       </c>
-      <c r="H27" s="5">
+      <c r="H27" s="6">
         <v>46273.683738425927</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="5">
         <v>46279</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L27" s="7"/>
-      <c r="M27" s="8"/>
-      <c r="AS27" s="8"/>
-      <c r="AT27" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L27" s="8"/>
+      <c r="M27" s="9"/>
+      <c r="AS27" s="9"/>
+      <c r="AT27" s="8"/>
     </row>
     <row r="28" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>2</v>
@@ -2172,38 +2203,38 @@
       <c r="D28" s="3">
         <v>36</v>
       </c>
-      <c r="E28" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F28" s="11">
+      <c r="E28" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F28" s="5">
         <v>46283</v>
       </c>
       <c r="G28" s="3">
         <v>24637</v>
       </c>
-      <c r="H28" s="5">
+      <c r="H28" s="6">
         <v>46274.288831018515</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="5">
         <v>46279</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="7"/>
-      <c r="M28" s="8"/>
-      <c r="AS28" s="8"/>
-      <c r="AT28" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L28" s="8"/>
+      <c r="M28" s="9"/>
+      <c r="AS28" s="9"/>
+      <c r="AT28" s="8"/>
     </row>
     <row r="29" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" s="3">
         <v>2026</v>
@@ -2211,39 +2242,39 @@
       <c r="D29" s="3">
         <v>36</v>
       </c>
-      <c r="E29" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F29" s="11">
+      <c r="E29" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F29" s="5">
         <v>46283</v>
       </c>
       <c r="G29" s="3">
         <v>24639</v>
       </c>
-      <c r="H29" s="5">
+      <c r="H29" s="6">
         <v>46274.312928240739</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="5">
         <v>46279</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K29" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="8"/>
-      <c r="O29" s="7"/>
-      <c r="AS29" s="8"/>
-      <c r="AT29" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L29" s="8"/>
+      <c r="M29" s="9"/>
+      <c r="O29" s="8"/>
+      <c r="AS29" s="9"/>
+      <c r="AT29" s="8"/>
     </row>
     <row r="30" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C30" s="3">
         <v>2026</v>
@@ -2251,36 +2282,36 @@
       <c r="D30" s="3">
         <v>36</v>
       </c>
-      <c r="E30" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F30" s="11">
+      <c r="E30" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F30" s="5">
         <v>46283</v>
       </c>
       <c r="G30" s="3">
         <v>24640</v>
       </c>
-      <c r="H30" s="5">
+      <c r="H30" s="6">
         <v>46274.319467592592</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="5">
         <v>46279</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="7"/>
-      <c r="M30" s="8"/>
-      <c r="O30" s="7"/>
-      <c r="AS30" s="8"/>
-      <c r="AT30" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L30" s="8"/>
+      <c r="M30" s="9"/>
+      <c r="O30" s="8"/>
+      <c r="AS30" s="9"/>
+      <c r="AT30" s="8"/>
     </row>
     <row r="31" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>2</v>
@@ -2291,35 +2322,35 @@
       <c r="D31" s="3">
         <v>36</v>
       </c>
-      <c r="E31" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F31" s="11">
+      <c r="E31" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F31" s="5">
         <v>46283</v>
       </c>
       <c r="G31" s="3">
         <v>24652</v>
       </c>
-      <c r="H31" s="5">
+      <c r="H31" s="6">
         <v>46274.379305555558</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="5">
         <v>46279</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K31" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L31" s="7"/>
-      <c r="M31" s="8"/>
-      <c r="AS31" s="8"/>
-      <c r="AT31" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K31" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L31" s="8"/>
+      <c r="M31" s="9"/>
+      <c r="AS31" s="9"/>
+      <c r="AT31" s="8"/>
     </row>
     <row r="32" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>2</v>
@@ -2330,35 +2361,35 @@
       <c r="D32" s="3">
         <v>36</v>
       </c>
-      <c r="E32" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F32" s="11">
+      <c r="E32" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F32" s="5">
         <v>46283</v>
       </c>
       <c r="G32" s="3">
         <v>24653</v>
       </c>
-      <c r="H32" s="5">
+      <c r="H32" s="6">
         <v>46274.379583333335</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="5">
         <v>46279</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="7"/>
-      <c r="M32" s="8"/>
-      <c r="AS32" s="8"/>
-      <c r="AT32" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="8"/>
+      <c r="M32" s="9"/>
+      <c r="AS32" s="9"/>
+      <c r="AT32" s="8"/>
     </row>
     <row r="33" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>2</v>
@@ -2369,36 +2400,36 @@
       <c r="D33" s="3">
         <v>36</v>
       </c>
-      <c r="E33" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F33" s="11">
+      <c r="E33" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F33" s="5">
         <v>46283</v>
       </c>
       <c r="G33" s="3">
         <v>24657</v>
       </c>
-      <c r="H33" s="5">
+      <c r="H33" s="6">
         <v>46274.389108796298</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="5">
         <v>46279</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="7"/>
-      <c r="M33" s="8"/>
-      <c r="O33" s="7"/>
-      <c r="AS33" s="8"/>
-      <c r="AT33" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L33" s="8"/>
+      <c r="M33" s="9"/>
+      <c r="O33" s="8"/>
+      <c r="AS33" s="9"/>
+      <c r="AT33" s="8"/>
     </row>
     <row r="34" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>2</v>
@@ -2409,35 +2440,35 @@
       <c r="D34" s="3">
         <v>36</v>
       </c>
-      <c r="E34" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F34" s="11">
+      <c r="E34" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F34" s="5">
         <v>46283</v>
       </c>
       <c r="G34" s="3">
         <v>24658</v>
       </c>
-      <c r="H34" s="5">
+      <c r="H34" s="6">
         <v>46274.389594907407</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="5">
         <v>46279</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="7"/>
-      <c r="M34" s="8"/>
-      <c r="AS34" s="8"/>
-      <c r="AT34" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K34" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" s="8"/>
+      <c r="M34" s="9"/>
+      <c r="AS34" s="9"/>
+      <c r="AT34" s="8"/>
     </row>
     <row r="35" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>2</v>
@@ -2448,35 +2479,35 @@
       <c r="D35" s="3">
         <v>36</v>
       </c>
-      <c r="E35" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F35" s="11">
+      <c r="E35" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F35" s="5">
         <v>46283</v>
       </c>
       <c r="G35" s="3">
         <v>24669</v>
       </c>
-      <c r="H35" s="5">
+      <c r="H35" s="6">
         <v>46274.419930555552</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="5">
         <v>46279</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K35" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="7"/>
-      <c r="M35" s="8"/>
-      <c r="AS35" s="8"/>
-      <c r="AT35" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L35" s="8"/>
+      <c r="M35" s="9"/>
+      <c r="AS35" s="9"/>
+      <c r="AT35" s="8"/>
     </row>
     <row r="36" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>2</v>
@@ -2487,35 +2518,35 @@
       <c r="D36" s="3">
         <v>36</v>
       </c>
-      <c r="E36" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F36" s="11">
+      <c r="E36" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F36" s="5">
         <v>46283</v>
       </c>
       <c r="G36" s="3">
         <v>24677</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H36" s="6">
         <v>46274.459409722222</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="5">
         <v>46279</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" s="7"/>
-      <c r="M36" s="8"/>
-      <c r="AS36" s="8"/>
-      <c r="AT36" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L36" s="8"/>
+      <c r="M36" s="9"/>
+      <c r="AS36" s="9"/>
+      <c r="AT36" s="8"/>
     </row>
     <row r="37" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>8</v>
@@ -2526,114 +2557,114 @@
       <c r="D37" s="3">
         <v>36</v>
       </c>
-      <c r="E37" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F37" s="11">
+      <c r="E37" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F37" s="5">
         <v>46283</v>
       </c>
       <c r="G37" s="3">
         <v>24526</v>
       </c>
-      <c r="H37" s="5">
+      <c r="H37" s="6">
         <v>46273.347256944442</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="5">
         <v>46279</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K37" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="7"/>
-      <c r="M37" s="8"/>
-      <c r="AS37" s="8"/>
-      <c r="AT37" s="7"/>
-    </row>
-    <row r="38" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B38" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L37" s="8"/>
+      <c r="M37" s="9"/>
+      <c r="AS37" s="9"/>
+      <c r="AT37" s="8"/>
+    </row>
+    <row r="38" spans="1:46" s="20" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D38" s="3">
-        <v>36</v>
-      </c>
-      <c r="E38" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F38" s="11">
-        <v>46283</v>
-      </c>
-      <c r="G38" s="3">
+      <c r="C38" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D38" s="13">
+        <v>36</v>
+      </c>
+      <c r="E38" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F38" s="15">
+        <v>46283</v>
+      </c>
+      <c r="G38" s="13">
         <v>21874</v>
       </c>
-      <c r="H38" s="5">
+      <c r="H38" s="16">
         <v>46230.419328703705</v>
       </c>
-      <c r="I38" s="11">
-        <v>46279</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" s="7"/>
-      <c r="M38" s="8"/>
-      <c r="AS38" s="8"/>
-      <c r="AT38" s="7"/>
-    </row>
-    <row r="39" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B39" s="4" t="s">
+      <c r="I38" s="15">
+        <v>46279</v>
+      </c>
+      <c r="J38" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="18"/>
+      <c r="M38" s="19"/>
+      <c r="AS38" s="19"/>
+      <c r="AT38" s="18"/>
+    </row>
+    <row r="39" spans="1:46" s="20" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C39" s="3">
-        <v>2026</v>
-      </c>
-      <c r="D39" s="3">
-        <v>36</v>
-      </c>
-      <c r="E39" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F39" s="11">
-        <v>46283</v>
-      </c>
-      <c r="G39" s="3">
+      <c r="C39" s="13">
+        <v>2026</v>
+      </c>
+      <c r="D39" s="13">
+        <v>36</v>
+      </c>
+      <c r="E39" s="15">
+        <v>46279</v>
+      </c>
+      <c r="F39" s="15">
+        <v>46283</v>
+      </c>
+      <c r="G39" s="13">
         <v>24465</v>
       </c>
-      <c r="H39" s="5">
+      <c r="H39" s="16">
         <v>46269.628449074073</v>
       </c>
-      <c r="I39" s="11">
-        <v>46279</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K39" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="7"/>
-      <c r="M39" s="8"/>
-      <c r="O39" s="7"/>
-      <c r="AS39" s="8"/>
-      <c r="AT39" s="7"/>
+      <c r="I39" s="15">
+        <v>46279</v>
+      </c>
+      <c r="J39" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" s="18"/>
+      <c r="M39" s="19"/>
+      <c r="O39" s="18"/>
+      <c r="AS39" s="19"/>
+      <c r="AT39" s="18"/>
     </row>
     <row r="40" spans="1:46" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>6</v>
@@ -2644,32 +2675,32 @@
       <c r="D40" s="3">
         <v>36</v>
       </c>
-      <c r="E40" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F40" s="11">
+      <c r="E40" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F40" s="5">
         <v>46283</v>
       </c>
       <c r="G40" s="3">
         <v>24404</v>
       </c>
-      <c r="H40" s="5">
+      <c r="H40" s="6">
         <v>46268.621388888889</v>
       </c>
-      <c r="I40" s="11">
+      <c r="I40" s="5">
         <v>46279</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L40" s="7"/>
-      <c r="M40" s="8"/>
-      <c r="O40" s="7"/>
-      <c r="AS40" s="8"/>
-      <c r="AT40" s="7"/>
+        <v>27</v>
+      </c>
+      <c r="K40" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="L40" s="8"/>
+      <c r="M40" s="9"/>
+      <c r="O40" s="8"/>
+      <c r="AS40" s="9"/>
+      <c r="AT40" s="8"/>
     </row>
     <row r="41" spans="1:46" x14ac:dyDescent="0.25">
       <c r="E41" s="12"/>
@@ -2679,7 +2710,7 @@
       <c r="E42" s="12"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{B327A729-0551-401F-B555-D8AED70D606E}">
+  <autoFilter ref="A1:K40" xr:uid="{B327A729-0551-401F-B555-D8AED70D606E}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K43">
       <sortCondition ref="B1"/>
     </sortState>
@@ -2690,63 +2721,64 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC11F51-DC51-461C-AA02-DA399D0E5568}">
-  <dimension ref="A1:AI15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" style="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.42578125" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3">
         <v>2026</v>
@@ -2754,34 +2786,34 @@
       <c r="D2" s="3">
         <v>36</v>
       </c>
-      <c r="E2" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F2" s="11">
+      <c r="E2" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F2" s="5">
         <v>46283</v>
       </c>
       <c r="G2" s="3">
         <v>22908</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="6">
         <v>46245.70453703704</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="5">
         <v>46279</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3">
         <v>2026</v>
@@ -2789,34 +2821,34 @@
       <c r="D3" s="3">
         <v>36</v>
       </c>
-      <c r="E3" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F3" s="11">
+      <c r="E3" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F3" s="5">
         <v>46283</v>
       </c>
       <c r="G3" s="3">
         <v>24123</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3" s="6">
         <v>46265.589861111112</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="5">
         <v>46279</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3">
         <v>2026</v>
@@ -2824,34 +2856,34 @@
       <c r="D4" s="3">
         <v>36</v>
       </c>
-      <c r="E4" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F4" s="11">
+      <c r="E4" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F4" s="5">
         <v>46283</v>
       </c>
       <c r="G4" s="3">
         <v>24182</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="6">
         <v>46266.384953703702</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="5">
         <v>46279</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" s="3">
         <v>2026</v>
@@ -2859,34 +2891,34 @@
       <c r="D5" s="3">
         <v>36</v>
       </c>
-      <c r="E5" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F5" s="11">
+      <c r="E5" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F5" s="5">
         <v>46283</v>
       </c>
       <c r="G5" s="3">
         <v>24307</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="6">
         <v>46267.605532407404</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="5">
         <v>46279</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3">
         <v>2026</v>
@@ -2894,34 +2926,34 @@
       <c r="D6" s="3">
         <v>36</v>
       </c>
-      <c r="E6" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F6" s="11">
+      <c r="E6" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F6" s="5">
         <v>46283</v>
       </c>
       <c r="G6" s="3">
         <v>24412</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="6">
         <v>46268.682766203703</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="5">
         <v>46279</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3">
         <v>2026</v>
@@ -2929,34 +2961,34 @@
       <c r="D7" s="3">
         <v>36</v>
       </c>
-      <c r="E7" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F7" s="11">
+      <c r="E7" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F7" s="5">
         <v>46283</v>
       </c>
       <c r="G7" s="3">
         <v>24511</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="6">
         <v>46273.295497685183</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="5">
         <v>46279</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3">
         <v>2026</v>
@@ -2964,55 +2996,55 @@
       <c r="D8" s="3">
         <v>36</v>
       </c>
-      <c r="E8" s="11">
-        <v>46279</v>
-      </c>
-      <c r="F8" s="11">
+      <c r="E8" s="5">
+        <v>46279</v>
+      </c>
+      <c r="F8" s="5">
         <v>46283</v>
       </c>
       <c r="G8" s="3">
         <v>24693</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8" s="6">
         <v>46274.568391203706</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="5">
         <v>46279</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>27</v>
+        <v>27</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{1EC11F51-DC51-461C-AA02-DA399D0E5568}"/>
